--- a/dossiers.xlsx
+++ b/dossiers.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="750" yWindow="570" windowWidth="17415" windowHeight="9150" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Dossiers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,9 +25,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00107C41"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,8 +44,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,14 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,8 +432,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B414"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -446,7 +451,2959 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VV1382</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VV1383</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VV1662</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VV1796</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VV1798</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VV1800</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VV1801</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VV1802</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VV1807</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VV1811</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VV1814</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VV1818</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VV1819</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VV1820</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VV1822</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VV1824</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VV1828</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VV1830</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VV1831</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VV1832</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VV1844</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VV1846</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VV1848</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VV1849</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VV1850</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VV1851</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VV1852</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VV1853</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VV1854</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VV1855</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VV1858</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VV1859</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>VV1860</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VV1861</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VV1862</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VV1864</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VV1865</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VV1867</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VV1870</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VV1874</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VV1875</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VV1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>VV1877</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>VV1878</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VV1883</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VV1884</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>VV1885</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VV1886</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>VV1887</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>VV1889</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VV1890</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VV1891</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VV1892</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VV1893</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VV1894</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VV1895</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VV1896</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VV1902</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>VV1903</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VV1906</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VV1908</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VV1909</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VV1910</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VV1911</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VV1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VV1913</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VV1914</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VV1915</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VV1916</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VV1917</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VV1918</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VV1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VV1921</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VV1923</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VV1924</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>VV1926</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>VV1927</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VV1928</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>VV1929</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VV1930</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>VV1931</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>VV1932</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>VV1933</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>VV1934</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VV1936</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>VV1937</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VV1938</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VV1939</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VV1940</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>VV1942</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>VV1943</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>VV1944</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>VV1945</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>VV1948</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>VV1949</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>VV1950</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>VV1951</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VV1952</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>VV1953</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>VV1954</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>VV1956</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>VV1958</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>VV1959</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>VV1960</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>VV1961</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>VV1963</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>VV1964</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>VV1965</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>VV1966</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>VV1972</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>VV1974</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>VV1979</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>VV1980</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>VV1981</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>VV1983</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>VV1984</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>VV1985</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>VV1986</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>VV1987</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>VV1988</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>VV1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>VV1990</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>VV1991</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>VV1992</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>VD1152</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>VD1374</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>VD1378</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>VD1381</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>VD1383</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>VD1384</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>VD1385</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>VD1386</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>VD1387</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VD1389</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>VD1390</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>VD1391</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>VD1393</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>VD1394</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>VD1396</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>VD1397</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>VD1398</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>VD1399</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>VD1400</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>VD1401</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>VD1402</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>VD1403</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>VD1404</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>VD1406</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>VD1407</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>VD1408</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>VD1409</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>VD1410</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>VD1411</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>VD1412</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>VD1414</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>VD1415</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>VD1416</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>VD1417</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>VD1418</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>VD1419</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>VD1420</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>VD1421</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>VD1422</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>VD1423</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>VD1425</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>VD1426</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>VD1427</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>VD1428</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>VD1430</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>VD1431</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>VD1432</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>VD1433</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>VD1435</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>VD1436</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>VD1438</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>VD1439</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>VD1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>VD1441</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>VD1442</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>VD1443</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>VD1444</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>VD1445</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>VD1446</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>VD1453</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>VD1454</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VD1448</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>VD1449</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>VD1450</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>VD1452</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>VD1457</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>VD1458</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>VD1459</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>VD1460</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>VD1461</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>VD1462</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>VD1463</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>VD1464</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>VD1465</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>VD1466</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>VD1467</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>VD1470</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>VD1471</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>VD1472</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>VD1473</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>VD1474</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>VD1475</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>VD1476</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>VD1477</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>VD1478</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>VD1479</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>VD1480</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>VD1481</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>VD1482</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>VD1483</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>VD1484</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>VD1485</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>VD1486</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>VD1487</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>VD1488</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>VD1489</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>VD1350</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>VD1490</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>VD1492</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>VD1495</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>VD1496</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>VD1497</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>VD1498</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>VD1499</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>VD1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>VD1503</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>VD1504</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>VD1505</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>VD1507</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>VD1509</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>VD1510</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>VD1511</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>VD1512</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>VD1514</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>VD1515</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>VD1516</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>VD1517</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>VD1518</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>VD1519</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>VD1520</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>VD1521</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>VD1522</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>VD1523</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>VD1524</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>VD1525</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>VD1526</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>VI1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>VI1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>VI1060</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>VI0785</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>VI1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>VV1810</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>VD1376</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>VI1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>VI1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>VI1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>VI1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>VI1074</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>VI1075</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>VI1076</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>VI1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>VI1078</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>VI1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>VI1081</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>VI1082</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>VI1083</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>VI1084</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>VI1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>VI1086</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>VI1087</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>VI1088</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>VI1089</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>VI1090</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>VI1091</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>VI1092</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>VI1093</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>VI1094</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>VI1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>VI1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>VI1099</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>VI1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>VI1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>VI1103</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>VI1104</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>VI1106</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>VI1107</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>VI1109</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>VI1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>VI1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>VI1112</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>VI1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>VI1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>VI1115</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>VI1117</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>VI1118</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>VI1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>VI1121</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>VI1122</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>VI1123</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>VI1124</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>VI1127</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>VI1128</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>VI1130</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>VI1131</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>VI1132</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>VI1134</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>VI1135</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>VI1136</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>VI1137</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>VI1138</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>VI1139</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>VI1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>VI1142</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>VI1143</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>VI1144</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>VI1145</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>VI1146</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>VI1147</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>VI1148</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>VI1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>VI1151</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>VI1152</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>VI1153</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>VI1154</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>VI1155</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>VI1156</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>VI1157</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>VI1158</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>VI1159</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>VI1160</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>VI1161</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>VI1162</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>VI1163</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>VI1164</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>VI1165</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>VI1166</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>VI1167</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>VI1169</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>VI1170</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>VI1172</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>VI1173</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>VI1174</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>VI1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>VI1177</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>VI1178</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>VI1179</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>VI1180</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>VI1181</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>VI1182</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>VI1183</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>VI1184</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>VI1185</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>VI1186</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>VI1187</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>VI1188</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>VI1189</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>VI1190</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>VI1191</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>VI1192</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>VI1193</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>VI1194</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>VI1195</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>VI1196</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>VI1198</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>VI1199</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>VI1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>VI1201</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>VI1202</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>VI1203</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>VI1205</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>VI1206</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>VI1207</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>VI1208</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>VI1209</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>VI1210</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>VI1211</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>VI1212</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>VI1213</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>VI1214</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>VI1215</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>VI1216</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>VI1217</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>VI1218</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>VI1219</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>VI1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>VI1221</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>VI1222</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>VI1223</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>VI1224</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>VI1226</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>VI1227</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>VI1228</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>VI1229</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>VI1231</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>VI1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>VI1233</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>VI1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>VI1235</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>VI1236</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>VI1237</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>VI1238</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>VI1239</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>VI1240</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>VI1241</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>VI1242</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>VI1243</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>VI1244</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>VI1245</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>VI1246</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/dossiers.xlsx
+++ b/dossiers.xlsx
@@ -601,6 +601,11 @@
           <t>VV1819</t>
         </is>
       </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -608,6 +613,11 @@
           <t>VV1820</t>
         </is>
       </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -615,6 +625,11 @@
           <t>VV1822</t>
         </is>
       </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -622,6 +637,11 @@
           <t>VV1824</t>
         </is>
       </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -629,6 +649,11 @@
           <t>VV1828</t>
         </is>
       </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -636,6 +661,11 @@
           <t>VV1830</t>
         </is>
       </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -643,6 +673,11 @@
           <t>VV1831</t>
         </is>
       </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -650,6 +685,11 @@
           <t>VV1832</t>
         </is>
       </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -657,11 +697,21 @@
           <t>VV1844</t>
         </is>
       </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>VV1846</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
         </is>
       </c>
     </row>

--- a/dossiers.xlsx
+++ b/dossiers.xlsx
@@ -721,6 +721,11 @@
           <t>VV1848</t>
         </is>
       </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -728,6 +733,11 @@
           <t>VV1849</t>
         </is>
       </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -735,6 +745,11 @@
           <t>VV1850</t>
         </is>
       </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -742,6 +757,11 @@
           <t>VV1851</t>
         </is>
       </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -749,6 +769,11 @@
           <t>VV1852</t>
         </is>
       </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -756,6 +781,11 @@
           <t>VV1853</t>
         </is>
       </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -770,6 +800,11 @@
           <t>VV1855</t>
         </is>
       </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -777,6 +812,11 @@
           <t>VV1858</t>
         </is>
       </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -784,6 +824,11 @@
           <t>VV1859</t>
         </is>
       </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -791,6 +836,11 @@
           <t>VV1860</t>
         </is>
       </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -798,6 +848,11 @@
           <t>VV1861</t>
         </is>
       </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -805,6 +860,11 @@
           <t>VV1862</t>
         </is>
       </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -812,6 +872,11 @@
           <t>VV1864</t>
         </is>
       </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -819,6 +884,11 @@
           <t>VV1865</t>
         </is>
       </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -826,6 +896,11 @@
           <t>VV1867</t>
         </is>
       </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -833,6 +908,11 @@
           <t>VV1870</t>
         </is>
       </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -840,6 +920,11 @@
           <t>VV1874</t>
         </is>
       </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -847,6 +932,11 @@
           <t>VV1875</t>
         </is>
       </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -854,11 +944,21 @@
           <t>VV1876</t>
         </is>
       </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
           <t>VV1877</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
         </is>
       </c>
     </row>

--- a/dossiers.xlsx
+++ b/dossiers.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,14 @@
     <font>
       <b val="1"/>
       <color rgb="00107C41"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000878F9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0016A34A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +69,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,6 +978,11 @@
           <t>VV1878</t>
         </is>
       </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -975,6 +990,11 @@
           <t>VV1883</t>
         </is>
       </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -982,6 +1002,11 @@
           <t>VV1884</t>
         </is>
       </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -989,6 +1014,11 @@
           <t>VV1885</t>
         </is>
       </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -996,6 +1026,11 @@
           <t>VV1886</t>
         </is>
       </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1003,6 +1038,11 @@
           <t>VV1887</t>
         </is>
       </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1010,6 +1050,11 @@
           <t>VV1889</t>
         </is>
       </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1017,6 +1062,11 @@
           <t>VV1890</t>
         </is>
       </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1024,6 +1074,11 @@
           <t>VV1891</t>
         </is>
       </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1031,6 +1086,11 @@
           <t>VV1892</t>
         </is>
       </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1038,6 +1098,11 @@
           <t>VV1893</t>
         </is>
       </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1045,6 +1110,11 @@
           <t>VV1894</t>
         </is>
       </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1052,6 +1122,11 @@
           <t>VV1895</t>
         </is>
       </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1059,11 +1134,21 @@
           <t>VV1896</t>
         </is>
       </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
           <t>VV1902</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>En cours</t>
         </is>
       </c>
     </row>
